--- a/data/sampling/coulter_counter/cc_data.xlsx
+++ b/data/sampling/coulter_counter/cc_data.xlsx
@@ -1,26 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Liam/Desktop/UW/paper2/github/data/sampling/coulter_counter/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD1E157-5A6D-EC48-AFCA-5EFFF56F0D14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB52396D-7178-6242-8257-00B267FBF074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3960" yWindow="-21000" windowWidth="31400" windowHeight="21000" xr2:uid="{B39D2D7F-1A8F-604A-BE83-9C1D6F1CE7C5}"/>
+    <workbookView xWindow="1500" yWindow="1400" windowWidth="27640" windowHeight="16680" xr2:uid="{A318637C-6BA0-464C-A436-5D04BE7948EE}"/>
   </bookViews>
   <sheets>
-    <sheet name="data" sheetId="2" r:id="rId1"/>
-    <sheet name="depth_calcs" sheetId="1" r:id="rId2"/>
+    <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -37,12 +33,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="10">
+  <si>
+    <t>230_4</t>
+  </si>
   <si>
     <t>section</t>
   </si>
   <si>
+    <t>228_4</t>
+  </si>
+  <si>
     <t>stick</t>
+  </si>
+  <si>
+    <t>LIC</t>
+  </si>
+  <si>
+    <t>RIC</t>
+  </si>
+  <si>
+    <t>stick3</t>
   </si>
   <si>
     <t>top_depth</t>
@@ -53,45 +64,12 @@
   <si>
     <t>mid_depth</t>
   </si>
-  <si>
-    <t>LIC</t>
-  </si>
-  <si>
-    <t>RIC</t>
-  </si>
-  <si>
-    <t>228_4</t>
-  </si>
-  <si>
-    <t>230_4</t>
-  </si>
-  <si>
-    <t>stick3</t>
-  </si>
-  <si>
-    <t>length</t>
-  </si>
-  <si>
-    <t>sample#</t>
-  </si>
-  <si>
-    <t>total_length</t>
-  </si>
-  <si>
-    <t>sum</t>
-  </si>
-  <si>
-    <t>cut_thickness</t>
-  </si>
-  <si>
-    <t>offset</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -103,6 +81,127 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -112,15 +211,188 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -128,16 +400,204 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -468,25 +928,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{358B9F90-030A-1B40-9FB7-EC40B8D50512}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21895D15-DC8A-9748-8F7D-B49D651133E2}">
   <dimension ref="A1:KS23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:305" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F1">
         <v>1</v>
@@ -1391,10 +1851,10 @@
     </row>
     <row r="2" spans="1:305" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2">
         <v>155.065</v>
@@ -1403,7 +1863,8 @@
         <v>155.095</v>
       </c>
       <c r="E2">
-        <v>155.08000000000001</v>
+        <f>(C2+D2)/2</f>
+        <v>155.07999999999998</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -2308,19 +2769,20 @@
     </row>
     <row r="3" spans="1:305" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>155.09578569999999</v>
+        <v>155.0958</v>
       </c>
       <c r="D3">
-        <v>155.12578569999999</v>
+        <v>155.1258</v>
       </c>
       <c r="E3">
-        <v>155.11078570000001</v>
+        <f t="shared" ref="E3:E23" si="0">(C3+D3)/2</f>
+        <v>155.11079999999998</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -3225,19 +3687,20 @@
     </row>
     <row r="4" spans="1:305" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>155.12657139999999</v>
+        <v>155.1266</v>
       </c>
       <c r="D4">
-        <v>155.15657139999999</v>
+        <v>155.1566</v>
       </c>
       <c r="E4">
-        <v>155.1415714</v>
+        <f t="shared" si="0"/>
+        <v>155.14159999999998</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -4142,19 +4605,20 @@
     </row>
     <row r="5" spans="1:305" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>155.15735710000001</v>
+        <v>155.1574</v>
       </c>
       <c r="D5">
-        <v>155.1973571</v>
+        <v>155.19739999999999</v>
       </c>
       <c r="E5">
-        <v>155.17735709999999</v>
+        <f t="shared" si="0"/>
+        <v>155.17739999999998</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -5059,19 +5523,20 @@
     </row>
     <row r="6" spans="1:305" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>155.19814289999999</v>
+        <v>155.19810000000001</v>
       </c>
       <c r="D6">
-        <v>155.2411429</v>
+        <v>155.24109999999999</v>
       </c>
       <c r="E6">
-        <v>155.2196429</v>
+        <f t="shared" si="0"/>
+        <v>155.21960000000001</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -5976,19 +6441,20 @@
     </row>
     <row r="7" spans="1:305" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>155.24192859999999</v>
+        <v>155.24189999999999</v>
       </c>
       <c r="D7">
-        <v>155.27742860000001</v>
+        <v>155.2774</v>
       </c>
       <c r="E7">
-        <v>155.2596786</v>
+        <f t="shared" si="0"/>
+        <v>155.25964999999999</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -6893,19 +7359,20 @@
     </row>
     <row r="8" spans="1:305" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>155.2782143</v>
+        <v>155.2782</v>
       </c>
       <c r="D8">
-        <v>155.3072143</v>
+        <v>155.30719999999999</v>
       </c>
       <c r="E8">
-        <v>155.2927143</v>
+        <f t="shared" si="0"/>
+        <v>155.2927</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -7810,10 +8277,10 @@
     </row>
     <row r="9" spans="1:305" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9">
         <v>155.30799999999999</v>
@@ -7822,7 +8289,8 @@
         <v>155.33799999999999</v>
       </c>
       <c r="E9">
-        <v>155.32300000000001</v>
+        <f t="shared" si="0"/>
+        <v>155.32299999999998</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -8727,19 +9195,20 @@
     </row>
     <row r="10" spans="1:305" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10">
-        <v>155.065</v>
+        <v>155.083</v>
       </c>
       <c r="D10">
-        <v>155.095</v>
+        <v>155.113</v>
       </c>
       <c r="E10">
-        <v>155.08000000000001</v>
+        <f t="shared" si="0"/>
+        <v>155.09800000000001</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -9644,19 +10113,20 @@
     </row>
     <row r="11" spans="1:305" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11">
-        <v>155.095786</v>
+        <v>155.11410000000001</v>
       </c>
       <c r="D11">
-        <v>155.12578600000001</v>
+        <v>155.14410000000001</v>
       </c>
       <c r="E11">
-        <v>155.11078599999999</v>
+        <f t="shared" si="0"/>
+        <v>155.12909999999999</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -10561,19 +11031,20 @@
     </row>
     <row r="12" spans="1:305" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>155.12657100000001</v>
+        <v>155.14519999999999</v>
       </c>
       <c r="D12">
-        <v>155.15657100000001</v>
+        <v>155.18170000000001</v>
       </c>
       <c r="E12">
-        <v>155.1415714</v>
+        <f t="shared" si="0"/>
+        <v>155.16345000000001</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -11478,19 +11949,20 @@
     </row>
     <row r="13" spans="1:305" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>155.15735699999999</v>
+        <v>155.18270000000001</v>
       </c>
       <c r="D13">
-        <v>155.19735700000001</v>
+        <v>155.21270000000001</v>
       </c>
       <c r="E13">
-        <v>155.177357</v>
+        <f t="shared" si="0"/>
+        <v>155.1977</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -12395,19 +12867,20 @@
     </row>
     <row r="14" spans="1:305" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14">
-        <v>155.19814299999999</v>
+        <v>155.21379999999999</v>
       </c>
       <c r="D14">
-        <v>155.24114299999999</v>
+        <v>155.24379999999999</v>
       </c>
       <c r="E14">
-        <v>155.21964299999999</v>
+        <f t="shared" si="0"/>
+        <v>155.22879999999998</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -13312,19 +13785,20 @@
     </row>
     <row r="15" spans="1:305" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15">
-        <v>155.241929</v>
+        <v>155.2449</v>
       </c>
       <c r="D15">
-        <v>155.27742900000001</v>
+        <v>155.28989999999999</v>
       </c>
       <c r="E15">
-        <v>155.25967900000001</v>
+        <f t="shared" si="0"/>
+        <v>155.26740000000001</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -14229,19 +14703,20 @@
     </row>
     <row r="16" spans="1:305" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16">
-        <v>155.27821399999999</v>
+        <v>155.291</v>
       </c>
       <c r="D16">
-        <v>155.30721399999999</v>
+        <v>155.333</v>
       </c>
       <c r="E16">
-        <v>155.29271399999999</v>
+        <f t="shared" si="0"/>
+        <v>155.31200000000001</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -15146,21 +15621,19 @@
     </row>
     <row r="17" spans="1:305" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C17">
-        <f>depth_calcs!C2</f>
         <v>156.80500000000001</v>
       </c>
       <c r="D17">
-        <f>depth_calcs!D2</f>
         <v>156.83600000000001</v>
       </c>
       <c r="E17">
-        <f>depth_calcs!E2</f>
+        <f t="shared" si="0"/>
         <v>156.82050000000001</v>
       </c>
       <c r="F17">
@@ -16066,21 +16539,19 @@
     </row>
     <row r="18" spans="1:305" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C18">
-        <f>depth_calcs!C3</f>
         <v>156.83750000000001</v>
       </c>
       <c r="D18">
-        <f>depth_calcs!D3</f>
         <v>156.86250000000001</v>
       </c>
       <c r="E18">
-        <f>depth_calcs!E3</f>
+        <f t="shared" si="0"/>
         <v>156.85000000000002</v>
       </c>
       <c r="F18">
@@ -16986,21 +17457,19 @@
     </row>
     <row r="19" spans="1:305" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C19">
-        <f>depth_calcs!C4</f>
         <v>156.864</v>
       </c>
       <c r="D19">
-        <f>depth_calcs!D4</f>
         <v>156.89400000000001</v>
       </c>
       <c r="E19">
-        <f>depth_calcs!E4</f>
+        <f t="shared" si="0"/>
         <v>156.87900000000002</v>
       </c>
       <c r="F19">
@@ -17906,21 +18375,19 @@
     </row>
     <row r="20" spans="1:305" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C20">
-        <f>depth_calcs!C5</f>
         <v>156.8955</v>
       </c>
       <c r="D20">
-        <f>depth_calcs!D5</f>
         <v>156.92449999999999</v>
       </c>
       <c r="E20">
-        <f>depth_calcs!E5</f>
+        <f t="shared" si="0"/>
         <v>156.91</v>
       </c>
       <c r="F20">
@@ -18826,21 +19293,19 @@
     </row>
     <row r="21" spans="1:305" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C21">
-        <f>depth_calcs!C6</f>
         <v>156.92599999999999</v>
       </c>
       <c r="D21">
-        <f>depth_calcs!D6</f>
         <v>156.95599999999999</v>
       </c>
       <c r="E21">
-        <f>depth_calcs!E6</f>
+        <f t="shared" si="0"/>
         <v>156.94099999999997</v>
       </c>
       <c r="F21">
@@ -19746,22 +20211,20 @@
     </row>
     <row r="22" spans="1:305" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C22">
-        <f>depth_calcs!C7</f>
-        <v>156.95749999999998</v>
+        <v>156.95750000000001</v>
       </c>
       <c r="D22">
-        <f>depth_calcs!D7</f>
-        <v>156.99349999999998</v>
+        <v>156.99350000000001</v>
       </c>
       <c r="E22">
-        <f>depth_calcs!E7</f>
-        <v>156.97549999999998</v>
+        <f t="shared" si="0"/>
+        <v>156.97550000000001</v>
       </c>
       <c r="F22">
         <v>6528</v>
@@ -20666,21 +21129,19 @@
     </row>
     <row r="23" spans="1:305" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C23">
-        <f>depth_calcs!C8</f>
-        <v>156.99499999999998</v>
+        <v>156.995</v>
       </c>
       <c r="D23">
-        <f>depth_calcs!D8</f>
         <v>157.04499999999999</v>
       </c>
       <c r="E23">
-        <f>depth_calcs!E8</f>
+        <f t="shared" si="0"/>
         <v>157.01999999999998</v>
       </c>
       <c r="F23">
@@ -21585,216 +22046,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3408F08F-2648-384A-AA9E-AB32A589F2F3}">
-  <dimension ref="A1:E26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>79</v>
-      </c>
-      <c r="B2">
-        <v>31</v>
-      </c>
-      <c r="C2">
-        <f>B25+B26/1000</f>
-        <v>156.80500000000001</v>
-      </c>
-      <c r="D2">
-        <f>C2+B2/1000</f>
-        <v>156.83600000000001</v>
-      </c>
-      <c r="E2">
-        <f>(C2+D2)/2</f>
-        <v>156.82050000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>80</v>
-      </c>
-      <c r="B3">
-        <v>25</v>
-      </c>
-      <c r="C3">
-        <f>D2+$B$24/1000</f>
-        <v>156.83750000000001</v>
-      </c>
-      <c r="D3">
-        <f>C3+B3/1000</f>
-        <v>156.86250000000001</v>
-      </c>
-      <c r="E3">
-        <f t="shared" ref="E3:E8" si="0">(C3+D3)/2</f>
-        <v>156.85000000000002</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>81</v>
-      </c>
-      <c r="B4">
-        <v>30</v>
-      </c>
-      <c r="C4">
-        <f t="shared" ref="C4:C8" si="1">D3+$B$24/1000</f>
-        <v>156.864</v>
-      </c>
-      <c r="D4">
-        <f t="shared" ref="D4:D8" si="2">C4+B4/1000</f>
-        <v>156.89400000000001</v>
-      </c>
-      <c r="E4">
-        <f t="shared" si="0"/>
-        <v>156.87900000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>82</v>
-      </c>
-      <c r="B5">
-        <v>29</v>
-      </c>
-      <c r="C5">
-        <f t="shared" si="1"/>
-        <v>156.8955</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="2"/>
-        <v>156.92449999999999</v>
-      </c>
-      <c r="E5">
-        <f t="shared" si="0"/>
-        <v>156.91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>83</v>
-      </c>
-      <c r="B6">
-        <v>30</v>
-      </c>
-      <c r="C6">
-        <f t="shared" si="1"/>
-        <v>156.92599999999999</v>
-      </c>
-      <c r="D6">
-        <f t="shared" si="2"/>
-        <v>156.95599999999999</v>
-      </c>
-      <c r="E6">
-        <f t="shared" si="0"/>
-        <v>156.94099999999997</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>84</v>
-      </c>
-      <c r="B7">
-        <v>36</v>
-      </c>
-      <c r="C7">
-        <f t="shared" si="1"/>
-        <v>156.95749999999998</v>
-      </c>
-      <c r="D7">
-        <f t="shared" si="2"/>
-        <v>156.99349999999998</v>
-      </c>
-      <c r="E7">
-        <f t="shared" si="0"/>
-        <v>156.97549999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>85</v>
-      </c>
-      <c r="B8">
-        <v>50</v>
-      </c>
-      <c r="C8">
-        <f t="shared" si="1"/>
-        <v>156.99499999999998</v>
-      </c>
-      <c r="D8">
-        <f t="shared" si="2"/>
-        <v>157.04499999999999</v>
-      </c>
-      <c r="E8">
-        <f t="shared" si="0"/>
-        <v>157.01999999999998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11">
-        <f>SUM(B2:B8)</f>
-        <v>231</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24">
-        <f>(B23-B11)  / 6</f>
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>2</v>
-      </c>
-      <c r="B25">
-        <v>156.77000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>